--- a/results/optA_20251016_200330/experiments/experiment_mp_idb_stages/analysis_option_a_summary/experiment_summary.xlsx
+++ b/results/optA_20251016_200330/experiments/experiment_mp_idb_stages/analysis_option_a_summary/experiment_summary.xlsx
@@ -507,7 +507,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['densenet121_focal', 'efficientnet_b1_focal', 'efficientnet_b0_focal', 'resnet50_focal', 'efficientnet_b2_focal', 'resnet101_focal']</t>
+          <t>['densenet121_focal', 'efficientnet_b0_focal', 'efficientnet_b1_focal', 'efficientnet_b2_focal', 'resnet101_focal', 'resnet50_focal']</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025-10-17 20:50:01</t>
+          <t>2025-10-27 02:13:30</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
